--- a/data/products/p-gsb-001/work/views/calc/Clear-Budget.xlsx
+++ b/data/products/p-gsb-001/work/views/calc/Clear-Budget.xlsx
@@ -1352,11 +1352,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5096548"/>
-        <c:axId val="52963682"/>
+        <c:axId val="25021963"/>
+        <c:axId val="1622228"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5096548"/>
+        <c:axId val="25021963"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1388,7 +1388,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52963682"/>
+        <c:crossAx val="1622228"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1396,7 +1396,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="52963682"/>
+        <c:axId val="1622228"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1438,7 +1438,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5096548"/>
+        <c:crossAx val="25021963"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1827,8 +1827,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>684720</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1037160</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
@@ -1858,7 +1858,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>858600</xdr:colOff>
+      <xdr:colOff>858240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>175320</xdr:rowOff>
     </xdr:to>
@@ -1868,7 +1868,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="2185200" y="4324320"/>
+        <a:off x="2960280" y="4324320"/>
         <a:ext cx="3959640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -13479,7 +13479,8 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>

--- a/data/products/p-gsb-001/work/views/calc/Clear-Budget.xlsx
+++ b/data/products/p-gsb-001/work/views/calc/Clear-Budget.xlsx
@@ -32,7 +32,7 @@
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">April!$B$2:$L$30</definedName>
     <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Area" vbProcedure="false">August!$B$2:$L$30</definedName>
     <definedName function="false" hidden="false" localSheetId="15" name="_xlnm.Print_Area" vbProcedure="false">Bills!$B$2:$Q$16</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$B$2:$I$37</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$B$2:$I$35</definedName>
     <definedName function="false" hidden="false" localSheetId="17" name="_xlnm.Print_Area" vbProcedure="false">'Debt payoff'!$B$2:$J$15</definedName>
     <definedName function="false" hidden="false" localSheetId="14" name="_xlnm.Print_Area" vbProcedure="false">December!$B$2:$L$30</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">February!$B$2:$L$30</definedName>
@@ -43,13 +43,13 @@
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">May!$B$2:$L$30</definedName>
     <definedName function="false" hidden="false" localSheetId="13" name="_xlnm.Print_Area" vbProcedure="false">November!$B$2:$L$30</definedName>
     <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Area" vbProcedure="false">October!$B$2:$L$30</definedName>
-    <definedName function="false" hidden="false" localSheetId="16" name="_xlnm.Print_Area" vbProcedure="false">'Paycheck plan'!$B$2:$F$32</definedName>
+    <definedName function="false" hidden="false" localSheetId="16" name="_xlnm.Print_Area" vbProcedure="false">'Paycheck plan'!$B$2:$J$32</definedName>
     <definedName function="false" hidden="false" localSheetId="18" name="_xlnm.Print_Area" vbProcedure="false">'Savings goals'!$B$2:$H$12</definedName>
     <definedName function="false" hidden="false" localSheetId="11" name="_xlnm.Print_Area" vbProcedure="false">September!$B$2:$L$30</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Setup!$B$2:$G$41</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Start here'!$B$2:$E$26</definedName>
+    <definedName function="false" hidden="false" name="BudgetYear" vbProcedure="false">Setup!$C$6</definedName>
     <definedName function="false" hidden="false" name="Categories" vbProcedure="false">Setup!$E$10:$E$39</definedName>
-    <definedName function="false" hidden="false" name="Year" vbProcedure="false">Setup!$C$6</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="177">
   <si>
     <t xml:space="preserve">Clear Budget</t>
   </si>
@@ -417,6 +417,9 @@
     <t xml:space="preserve">Shoes</t>
   </si>
   <si>
+    <t xml:space="preserve">Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mark each bill paid with a ✓ from the dropdown.</t>
   </si>
   <si>
@@ -480,7 +483,7 @@
     <t xml:space="preserve">Paycheck plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Paid weekly or every two weeks? See which bills each paycheck covers. Paid monthly? Skip this tab.</t>
+    <t xml:space="preserve">Paid weekly, every two weeks or twice a month? See which bills each paycheck covers. Paid monthly? Skip this tab.</t>
   </si>
   <si>
     <t xml:space="preserve">Next payday</t>
@@ -549,6 +552,9 @@
     <t xml:space="preserve">Interest saved</t>
   </si>
   <si>
+    <t xml:space="preserve">Medical bill</t>
+  </si>
+  <si>
     <t xml:space="preserve">Car loan</t>
   </si>
   <si>
@@ -579,6 +585,9 @@
     <t xml:space="preserve">Save per month</t>
   </si>
   <si>
+    <t xml:space="preserve">Progress bar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Holiday trip</t>
   </si>
   <si>
@@ -589,17 +598,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00;[RED]&quot;-$&quot;#,##0.00;\$0.00"/>
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="\$#,##0"/>
     <numFmt numFmtId="168" formatCode="0"/>
     <numFmt numFmtId="169" formatCode="mmm\ d"/>
-    <numFmt numFmtId="170" formatCode="mmm\ d&quot;, &quot;yyyy"/>
-    <numFmt numFmtId="171" formatCode="ddd\ mmm\ d"/>
-    <numFmt numFmtId="172" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="mmm\ yyyy"/>
+    <numFmt numFmtId="170" formatCode="General"/>
+    <numFmt numFmtId="171" formatCode="mmm\ d&quot;, &quot;yyyy"/>
+    <numFmt numFmtId="172" formatCode="ddd\ mmm\ d"/>
+    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="174" formatCode="mmm\ yyyy"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -734,15 +744,15 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -830,7 +840,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -963,7 +973,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -971,11 +981,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="171" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -983,7 +993,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="173" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -991,9 +1001,13 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="174" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1103,19 +1117,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
               <a:t>Income and spending by month</a:t>
             </a:r>
@@ -1352,11 +1366,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="25021963"/>
-        <c:axId val="1622228"/>
+        <c:axId val="14989513"/>
+        <c:axId val="2526117"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25021963"/>
+        <c:axId val="14989513"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1379,16 +1393,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1622228"/>
+        <c:crossAx val="2526117"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1396,7 +1410,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1622228"/>
+        <c:axId val="2526117"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1429,16 +1443,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25021963"/>
+        <c:crossAx val="14989513"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1463,11 +1477,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -1502,19 +1516,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
               <a:t>Where the money went</a:t>
             </a:r>
@@ -1608,11 +1622,11 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -1633,11 +1647,11 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -1658,11 +1672,11 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -1683,11 +1697,11 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -1706,11 +1720,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -1790,11 +1804,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -1830,7 +1844,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>1037160</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>32760</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1838,7 +1852,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="211320" y="7419960"/>
+        <a:off x="211320" y="9048600"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1859,8 +1873,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>858240</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>175320</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>42120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1868,7 +1882,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="2960280" y="4324320"/>
+        <a:off x="2960280" y="5153040"/>
         <a:ext cx="3959640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2286,7 +2300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C13" s="10" t="s">
         <v>29</v>
       </c>
@@ -2633,7 +2647,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2683,7 +2697,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -2707,7 +2721,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -2720,7 +2734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -2733,7 +2747,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -2746,13 +2760,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -2774,7 +2788,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -2804,7 +2818,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -2834,7 +2848,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -2864,7 +2878,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -2894,7 +2908,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -2924,7 +2938,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -2954,7 +2968,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -2984,7 +2998,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -3014,7 +3028,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -3044,7 +3058,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -3074,7 +3088,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -3104,7 +3118,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -3134,7 +3148,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -3164,7 +3178,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -3194,7 +3208,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -3224,7 +3238,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -3254,7 +3268,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -3284,7 +3298,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -3314,7 +3328,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -3344,7 +3358,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -3374,7 +3388,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -3404,7 +3418,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -3434,7 +3448,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -3464,7 +3478,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -3494,7 +3508,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -3524,7 +3538,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -3554,7 +3568,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -3584,7 +3598,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -3614,7 +3628,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -3644,7 +3658,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -3674,275 +3688,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -3992,7 +4011,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -4042,7 +4061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -4066,7 +4085,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -4079,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -4092,7 +4111,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -4105,13 +4124,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -4133,7 +4152,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -4163,7 +4182,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -4193,7 +4212,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -4223,7 +4242,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -4253,7 +4272,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -4283,7 +4302,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -4313,7 +4332,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -4343,7 +4362,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -4373,7 +4392,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -4403,7 +4422,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -4433,7 +4452,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -4463,7 +4482,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -4493,7 +4512,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -4523,7 +4542,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -4553,7 +4572,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -4583,7 +4602,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -4613,7 +4632,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -4643,7 +4662,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -4673,7 +4692,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -4703,7 +4722,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -4733,7 +4752,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -4763,7 +4782,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -4793,7 +4812,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -4823,7 +4842,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -4853,7 +4872,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -4883,7 +4902,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -4913,7 +4932,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -4943,7 +4962,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -4973,7 +4992,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -5003,7 +5022,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -5033,275 +5052,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -5351,7 +5375,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -5401,7 +5425,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -5425,7 +5449,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -5438,7 +5462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -5451,7 +5475,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -5464,13 +5488,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -5492,7 +5516,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -5522,7 +5546,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -5552,7 +5576,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -5582,7 +5606,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -5612,7 +5636,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -5642,7 +5666,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -5672,7 +5696,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -5702,7 +5726,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -5732,7 +5756,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -5762,7 +5786,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -5792,7 +5816,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -5822,7 +5846,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -5852,7 +5876,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -5882,7 +5906,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -5912,7 +5936,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -5942,7 +5966,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -5972,7 +5996,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -6002,7 +6026,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -6032,7 +6056,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -6062,7 +6086,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -6092,7 +6116,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -6122,7 +6146,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -6152,7 +6176,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -6182,7 +6206,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -6212,7 +6236,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -6242,7 +6266,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -6272,7 +6296,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -6302,7 +6326,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -6332,7 +6356,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -6362,7 +6386,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -6392,275 +6416,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -6710,7 +6739,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -6760,7 +6789,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -6784,7 +6813,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -6797,7 +6826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -6810,7 +6839,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -6823,13 +6852,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -6851,7 +6880,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -6881,7 +6910,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -6911,7 +6940,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -6941,7 +6970,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -6971,7 +7000,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -7001,7 +7030,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -7031,7 +7060,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -7061,7 +7090,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -7091,7 +7120,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -7121,7 +7150,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -7151,7 +7180,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -7181,7 +7210,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -7211,7 +7240,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -7241,7 +7270,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -7271,7 +7300,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -7301,7 +7330,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -7331,7 +7360,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -7361,7 +7390,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -7391,7 +7420,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -7421,7 +7450,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -7451,7 +7480,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -7481,7 +7510,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -7511,7 +7540,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -7541,7 +7570,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -7571,7 +7600,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -7601,7 +7630,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -7631,7 +7660,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -7661,7 +7690,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -7691,7 +7720,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -7721,7 +7750,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -7751,275 +7780,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -8069,7 +8103,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -8119,7 +8153,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -8143,7 +8177,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -8156,7 +8190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -8169,7 +8203,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -8182,13 +8216,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -8210,7 +8244,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -8240,7 +8274,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -8270,7 +8304,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -8300,7 +8334,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -8330,7 +8364,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -8360,7 +8394,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -8390,7 +8424,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -8420,7 +8454,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -8450,7 +8484,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -8480,7 +8514,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -8510,7 +8544,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -8540,7 +8574,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -8570,7 +8604,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -8600,7 +8634,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -8630,7 +8664,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -8660,7 +8694,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -8690,7 +8724,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -8720,7 +8754,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -8750,7 +8784,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -8780,7 +8814,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -8810,7 +8844,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -8840,7 +8874,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -8870,7 +8904,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -8900,7 +8934,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -8930,7 +8964,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -8960,7 +8994,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -8990,7 +9024,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -9020,7 +9054,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -9050,7 +9084,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -9080,7 +9114,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -9110,275 +9144,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -9428,7 +9467,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -9478,7 +9517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -9502,7 +9541,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -9515,7 +9554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -9528,7 +9567,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -9541,13 +9580,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -9569,7 +9608,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -9599,7 +9638,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -9629,7 +9668,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -9659,7 +9698,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -9689,7 +9728,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -9719,7 +9758,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -9749,7 +9788,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -9779,7 +9818,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -9809,7 +9848,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -9839,7 +9878,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -9869,7 +9908,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -9899,7 +9938,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -9929,7 +9968,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -9959,7 +9998,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -9989,7 +10028,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -10019,7 +10058,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -10049,7 +10088,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -10079,7 +10118,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -10109,7 +10148,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -10139,7 +10178,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -10169,7 +10208,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -10199,7 +10238,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -10229,7 +10268,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -10259,7 +10298,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -10289,7 +10328,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -10319,7 +10358,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -10349,7 +10388,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -10379,7 +10418,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -10409,7 +10448,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -10439,7 +10478,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -10469,275 +10508,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -10806,7 +10850,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10835,54 +10879,54 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>102</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>24</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q6" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10896,7 +10940,7 @@
         <v>1400</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34"/>
@@ -10922,7 +10966,7 @@
         <v>95</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
@@ -10948,7 +10992,7 @@
         <v>15.99</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -10965,7 +11009,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>20</v>
@@ -10974,7 +11018,7 @@
         <v>160</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34"/>
@@ -10991,7 +11035,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>22</v>
@@ -11000,7 +11044,7 @@
         <v>90</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34"/>
@@ -11026,7 +11070,7 @@
         <v>150</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F12" s="34"/>
       <c r="G12" s="34"/>
@@ -11385,7 +11429,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D32" s="23" t="n">
         <f aca="false">SUM(D7:D31)</f>
@@ -11441,12 +11485,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11477,48 +11521,48 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C6" s="35" t="n">
-        <f aca="false">DATE(Year,1,1)+MOD(6-WEEKDAY(DATE(Year,1,1)),7)</f>
+        <f aca="false">DATE(BudgetYear,1,1)+MOD(6-WEEKDAY(DATE(BudgetYear,1,1)),7)</f>
         <v>46388</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C8" s="26" t="n">
         <f aca="false">ROUND(Setup!$C$10*12/CHOOSE(MATCH($C$7,{"Weekly","Every 2 weeks","Twice a month","Monthly"},0),52,26,24,12),2)</f>
         <v>1661.54</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11545,7 +11589,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="36" t="n">
-        <f aca="false">IF(F11="","",IF(F11&gt;DATE(Year,12,31),"",F11))</f>
+        <f aca="false">IF(F11="","",IF(F11&gt;DATE(BudgetYear,12,31),"",F11))</f>
         <v>46402</v>
       </c>
       <c r="C12" s="26" t="n">
@@ -11567,7 +11611,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="36" t="n">
-        <f aca="false">IF(F12="","",IF(F12&gt;DATE(Year,12,31),"",F12))</f>
+        <f aca="false">IF(F12="","",IF(F12&gt;DATE(BudgetYear,12,31),"",F12))</f>
         <v>46416</v>
       </c>
       <c r="C13" s="26" t="n">
@@ -11589,7 +11633,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="36" t="n">
-        <f aca="false">IF(F13="","",IF(F13&gt;DATE(Year,12,31),"",F13))</f>
+        <f aca="false">IF(F13="","",IF(F13&gt;DATE(BudgetYear,12,31),"",F13))</f>
         <v>46430</v>
       </c>
       <c r="C14" s="26" t="n">
@@ -11611,7 +11655,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="36" t="n">
-        <f aca="false">IF(F14="","",IF(F14&gt;DATE(Year,12,31),"",F14))</f>
+        <f aca="false">IF(F14="","",IF(F14&gt;DATE(BudgetYear,12,31),"",F14))</f>
         <v>46444</v>
       </c>
       <c r="C15" s="26" t="n">
@@ -11633,7 +11677,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="36" t="n">
-        <f aca="false">IF(F15="","",IF(F15&gt;DATE(Year,12,31),"",F15))</f>
+        <f aca="false">IF(F15="","",IF(F15&gt;DATE(BudgetYear,12,31),"",F15))</f>
         <v>46458</v>
       </c>
       <c r="C16" s="26" t="n">
@@ -11655,7 +11699,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="36" t="n">
-        <f aca="false">IF(F16="","",IF(F16&gt;DATE(Year,12,31),"",F16))</f>
+        <f aca="false">IF(F16="","",IF(F16&gt;DATE(BudgetYear,12,31),"",F16))</f>
         <v>46472</v>
       </c>
       <c r="C17" s="26" t="n">
@@ -11677,7 +11721,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="36" t="n">
-        <f aca="false">IF(F17="","",IF(F17&gt;DATE(Year,12,31),"",F17))</f>
+        <f aca="false">IF(F17="","",IF(F17&gt;DATE(BudgetYear,12,31),"",F17))</f>
         <v>46486</v>
       </c>
       <c r="C18" s="26" t="n">
@@ -11699,7 +11743,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="36" t="n">
-        <f aca="false">IF(F18="","",IF(F18&gt;DATE(Year,12,31),"",F18))</f>
+        <f aca="false">IF(F18="","",IF(F18&gt;DATE(BudgetYear,12,31),"",F18))</f>
         <v>46500</v>
       </c>
       <c r="C19" s="26" t="n">
@@ -11721,7 +11765,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="36" t="n">
-        <f aca="false">IF(F19="","",IF(F19&gt;DATE(Year,12,31),"",F19))</f>
+        <f aca="false">IF(F19="","",IF(F19&gt;DATE(BudgetYear,12,31),"",F19))</f>
         <v>46514</v>
       </c>
       <c r="C20" s="26" t="n">
@@ -11743,7 +11787,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="36" t="n">
-        <f aca="false">IF(F20="","",IF(F20&gt;DATE(Year,12,31),"",F20))</f>
+        <f aca="false">IF(F20="","",IF(F20&gt;DATE(BudgetYear,12,31),"",F20))</f>
         <v>46528</v>
       </c>
       <c r="C21" s="26" t="n">
@@ -11765,7 +11809,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="36" t="n">
-        <f aca="false">IF(F21="","",IF(F21&gt;DATE(Year,12,31),"",F21))</f>
+        <f aca="false">IF(F21="","",IF(F21&gt;DATE(BudgetYear,12,31),"",F21))</f>
         <v>46542</v>
       </c>
       <c r="C22" s="26" t="n">
@@ -11787,7 +11831,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="36" t="n">
-        <f aca="false">IF(F22="","",IF(F22&gt;DATE(Year,12,31),"",F22))</f>
+        <f aca="false">IF(F22="","",IF(F22&gt;DATE(BudgetYear,12,31),"",F22))</f>
         <v>46556</v>
       </c>
       <c r="C23" s="26" t="n">
@@ -11809,7 +11853,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="36" t="n">
-        <f aca="false">IF(F23="","",IF(F23&gt;DATE(Year,12,31),"",F23))</f>
+        <f aca="false">IF(F23="","",IF(F23&gt;DATE(BudgetYear,12,31),"",F23))</f>
         <v>46570</v>
       </c>
       <c r="C24" s="26" t="n">
@@ -11831,7 +11875,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="36" t="n">
-        <f aca="false">IF(F24="","",IF(F24&gt;DATE(Year,12,31),"",F24))</f>
+        <f aca="false">IF(F24="","",IF(F24&gt;DATE(BudgetYear,12,31),"",F24))</f>
         <v>46584</v>
       </c>
       <c r="C25" s="26" t="n">
@@ -11853,7 +11897,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="36" t="n">
-        <f aca="false">IF(F25="","",IF(F25&gt;DATE(Year,12,31),"",F25))</f>
+        <f aca="false">IF(F25="","",IF(F25&gt;DATE(BudgetYear,12,31),"",F25))</f>
         <v>46598</v>
       </c>
       <c r="C26" s="26" t="n">
@@ -11875,7 +11919,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="36" t="n">
-        <f aca="false">IF(F26="","",IF(F26&gt;DATE(Year,12,31),"",F26))</f>
+        <f aca="false">IF(F26="","",IF(F26&gt;DATE(BudgetYear,12,31),"",F26))</f>
         <v>46612</v>
       </c>
       <c r="C27" s="26" t="n">
@@ -11897,7 +11941,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="36" t="n">
-        <f aca="false">IF(F27="","",IF(F27&gt;DATE(Year,12,31),"",F27))</f>
+        <f aca="false">IF(F27="","",IF(F27&gt;DATE(BudgetYear,12,31),"",F27))</f>
         <v>46626</v>
       </c>
       <c r="C28" s="26" t="n">
@@ -11919,7 +11963,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="36" t="n">
-        <f aca="false">IF(F28="","",IF(F28&gt;DATE(Year,12,31),"",F28))</f>
+        <f aca="false">IF(F28="","",IF(F28&gt;DATE(BudgetYear,12,31),"",F28))</f>
         <v>46640</v>
       </c>
       <c r="C29" s="26" t="n">
@@ -11941,7 +11985,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="36" t="n">
-        <f aca="false">IF(F29="","",IF(F29&gt;DATE(Year,12,31),"",F29))</f>
+        <f aca="false">IF(F29="","",IF(F29&gt;DATE(BudgetYear,12,31),"",F29))</f>
         <v>46654</v>
       </c>
       <c r="C30" s="26" t="n">
@@ -11963,7 +12007,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="36" t="n">
-        <f aca="false">IF(F30="","",IF(F30&gt;DATE(Year,12,31),"",F30))</f>
+        <f aca="false">IF(F30="","",IF(F30&gt;DATE(BudgetYear,12,31),"",F30))</f>
         <v>46668</v>
       </c>
       <c r="C31" s="26" t="n">
@@ -11985,7 +12029,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="36" t="n">
-        <f aca="false">IF(F31="","",IF(F31&gt;DATE(Year,12,31),"",F31))</f>
+        <f aca="false">IF(F31="","",IF(F31&gt;DATE(BudgetYear,12,31),"",F31))</f>
         <v>46682</v>
       </c>
       <c r="C32" s="26" t="n">
@@ -12007,7 +12051,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="36" t="n">
-        <f aca="false">IF(F32="","",IF(F32&gt;DATE(Year,12,31),"",F32))</f>
+        <f aca="false">IF(F32="","",IF(F32&gt;DATE(BudgetYear,12,31),"",F32))</f>
         <v>46696</v>
       </c>
       <c r="C33" s="26" t="n">
@@ -12029,7 +12073,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="36" t="n">
-        <f aca="false">IF(F33="","",IF(F33&gt;DATE(Year,12,31),"",F33))</f>
+        <f aca="false">IF(F33="","",IF(F33&gt;DATE(BudgetYear,12,31),"",F33))</f>
         <v>46710</v>
       </c>
       <c r="C34" s="26" t="n">
@@ -12051,7 +12095,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="36" t="n">
-        <f aca="false">IF(F34="","",IF(F34&gt;DATE(Year,12,31),"",F34))</f>
+        <f aca="false">IF(F34="","",IF(F34&gt;DATE(BudgetYear,12,31),"",F34))</f>
         <v>46724</v>
       </c>
       <c r="C35" s="26" t="n">
@@ -12073,7 +12117,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="36" t="n">
-        <f aca="false">IF(F35="","",IF(F35&gt;DATE(Year,12,31),"",F35))</f>
+        <f aca="false">IF(F35="","",IF(F35&gt;DATE(BudgetYear,12,31),"",F35))</f>
         <v>46738</v>
       </c>
       <c r="C36" s="26" t="n">
@@ -12095,7 +12139,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="36" t="n">
-        <f aca="false">IF(F36="","",IF(F36&gt;DATE(Year,12,31),"",F36))</f>
+        <f aca="false">IF(F36="","",IF(F36&gt;DATE(BudgetYear,12,31),"",F36))</f>
         <v>46752</v>
       </c>
       <c r="C37" s="26" t="n">
@@ -12117,7 +12161,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="36" t="str">
-        <f aca="false">IF(F37="","",IF(F37&gt;DATE(Year,12,31),"",F37))</f>
+        <f aca="false">IF(F37="","",IF(F37&gt;DATE(BudgetYear,12,31),"",F37))</f>
         <v/>
       </c>
       <c r="C38" s="26" t="str">
@@ -12139,7 +12183,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="36" t="str">
-        <f aca="false">IF(F38="","",IF(F38&gt;DATE(Year,12,31),"",F38))</f>
+        <f aca="false">IF(F38="","",IF(F38&gt;DATE(BudgetYear,12,31),"",F38))</f>
         <v/>
       </c>
       <c r="C39" s="26" t="str">
@@ -12161,7 +12205,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="36" t="str">
-        <f aca="false">IF(F39="","",IF(F39&gt;DATE(Year,12,31),"",F39))</f>
+        <f aca="false">IF(F39="","",IF(F39&gt;DATE(BudgetYear,12,31),"",F39))</f>
         <v/>
       </c>
       <c r="C40" s="26" t="str">
@@ -12183,7 +12227,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="36" t="str">
-        <f aca="false">IF(F40="","",IF(F40&gt;DATE(Year,12,31),"",F40))</f>
+        <f aca="false">IF(F40="","",IF(F40&gt;DATE(BudgetYear,12,31),"",F40))</f>
         <v/>
       </c>
       <c r="C41" s="26" t="str">
@@ -12205,7 +12249,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="36" t="str">
-        <f aca="false">IF(F41="","",IF(F41&gt;DATE(Year,12,31),"",F41))</f>
+        <f aca="false">IF(F41="","",IF(F41&gt;DATE(BudgetYear,12,31),"",F41))</f>
         <v/>
       </c>
       <c r="C42" s="26" t="str">
@@ -12227,7 +12271,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="36" t="str">
-        <f aca="false">IF(F42="","",IF(F42&gt;DATE(Year,12,31),"",F42))</f>
+        <f aca="false">IF(F42="","",IF(F42&gt;DATE(BudgetYear,12,31),"",F42))</f>
         <v/>
       </c>
       <c r="C43" s="26" t="str">
@@ -12249,7 +12293,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="36" t="str">
-        <f aca="false">IF(F43="","",IF(F43&gt;DATE(Year,12,31),"",F43))</f>
+        <f aca="false">IF(F43="","",IF(F43&gt;DATE(BudgetYear,12,31),"",F43))</f>
         <v/>
       </c>
       <c r="C44" s="26" t="str">
@@ -12271,7 +12315,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="36" t="str">
-        <f aca="false">IF(F44="","",IF(F44&gt;DATE(Year,12,31),"",F44))</f>
+        <f aca="false">IF(F44="","",IF(F44&gt;DATE(BudgetYear,12,31),"",F44))</f>
         <v/>
       </c>
       <c r="C45" s="26" t="str">
@@ -12293,7 +12337,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="36" t="str">
-        <f aca="false">IF(F45="","",IF(F45&gt;DATE(Year,12,31),"",F45))</f>
+        <f aca="false">IF(F45="","",IF(F45&gt;DATE(BudgetYear,12,31),"",F45))</f>
         <v/>
       </c>
       <c r="C46" s="26" t="str">
@@ -12315,7 +12359,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="36" t="str">
-        <f aca="false">IF(F46="","",IF(F46&gt;DATE(Year,12,31),"",F46))</f>
+        <f aca="false">IF(F46="","",IF(F46&gt;DATE(BudgetYear,12,31),"",F46))</f>
         <v/>
       </c>
       <c r="C47" s="26" t="str">
@@ -12337,7 +12381,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="36" t="str">
-        <f aca="false">IF(F47="","",IF(F47&gt;DATE(Year,12,31),"",F47))</f>
+        <f aca="false">IF(F47="","",IF(F47&gt;DATE(BudgetYear,12,31),"",F47))</f>
         <v/>
       </c>
       <c r="C48" s="26" t="str">
@@ -12359,7 +12403,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="36" t="str">
-        <f aca="false">IF(F48="","",IF(F48&gt;DATE(Year,12,31),"",F48))</f>
+        <f aca="false">IF(F48="","",IF(F48&gt;DATE(BudgetYear,12,31),"",F48))</f>
         <v/>
       </c>
       <c r="C49" s="26" t="str">
@@ -12381,7 +12425,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="36" t="str">
-        <f aca="false">IF(F49="","",IF(F49&gt;DATE(Year,12,31),"",F49))</f>
+        <f aca="false">IF(F49="","",IF(F49&gt;DATE(BudgetYear,12,31),"",F49))</f>
         <v/>
       </c>
       <c r="C50" s="26" t="str">
@@ -12403,7 +12447,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="36" t="str">
-        <f aca="false">IF(F50="","",IF(F50&gt;DATE(Year,12,31),"",F50))</f>
+        <f aca="false">IF(F50="","",IF(F50&gt;DATE(BudgetYear,12,31),"",F50))</f>
         <v/>
       </c>
       <c r="C51" s="26" t="str">
@@ -12425,7 +12469,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="36" t="str">
-        <f aca="false">IF(F51="","",IF(F51&gt;DATE(Year,12,31),"",F51))</f>
+        <f aca="false">IF(F51="","",IF(F51&gt;DATE(BudgetYear,12,31),"",F51))</f>
         <v/>
       </c>
       <c r="C52" s="26" t="str">
@@ -12447,7 +12491,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="36" t="str">
-        <f aca="false">IF(F52="","",IF(F52&gt;DATE(Year,12,31),"",F52))</f>
+        <f aca="false">IF(F52="","",IF(F52&gt;DATE(BudgetYear,12,31),"",F52))</f>
         <v/>
       </c>
       <c r="C53" s="26" t="str">
@@ -12469,7 +12513,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="36" t="str">
-        <f aca="false">IF(F53="","",IF(F53&gt;DATE(Year,12,31),"",F53))</f>
+        <f aca="false">IF(F53="","",IF(F53&gt;DATE(BudgetYear,12,31),"",F53))</f>
         <v/>
       </c>
       <c r="C54" s="26" t="str">
@@ -12491,7 +12535,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="36" t="str">
-        <f aca="false">IF(F54="","",IF(F54&gt;DATE(Year,12,31),"",F54))</f>
+        <f aca="false">IF(F54="","",IF(F54&gt;DATE(BudgetYear,12,31),"",F54))</f>
         <v/>
       </c>
       <c r="C55" s="26" t="str">
@@ -12513,7 +12557,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="36" t="str">
-        <f aca="false">IF(F55="","",IF(F55&gt;DATE(Year,12,31),"",F55))</f>
+        <f aca="false">IF(F55="","",IF(F55&gt;DATE(BudgetYear,12,31),"",F55))</f>
         <v/>
       </c>
       <c r="C56" s="26" t="str">
@@ -12535,7 +12579,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="36" t="str">
-        <f aca="false">IF(F56="","",IF(F56&gt;DATE(Year,12,31),"",F56))</f>
+        <f aca="false">IF(F56="","",IF(F56&gt;DATE(BudgetYear,12,31),"",F56))</f>
         <v/>
       </c>
       <c r="C57" s="26" t="str">
@@ -12557,7 +12601,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="36" t="str">
-        <f aca="false">IF(F57="","",IF(F57&gt;DATE(Year,12,31),"",F57))</f>
+        <f aca="false">IF(F57="","",IF(F57&gt;DATE(BudgetYear,12,31),"",F57))</f>
         <v/>
       </c>
       <c r="C58" s="26" t="str">
@@ -12579,7 +12623,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="36" t="str">
-        <f aca="false">IF(F58="","",IF(F58&gt;DATE(Year,12,31),"",F58))</f>
+        <f aca="false">IF(F58="","",IF(F58&gt;DATE(BudgetYear,12,31),"",F58))</f>
         <v/>
       </c>
       <c r="C59" s="26" t="str">
@@ -12601,7 +12645,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="36" t="str">
-        <f aca="false">IF(F59="","",IF(F59&gt;DATE(Year,12,31),"",F59))</f>
+        <f aca="false">IF(F59="","",IF(F59&gt;DATE(BudgetYear,12,31),"",F59))</f>
         <v/>
       </c>
       <c r="C60" s="26" t="str">
@@ -12623,7 +12667,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="36" t="str">
-        <f aca="false">IF(F60="","",IF(F60&gt;DATE(Year,12,31),"",F60))</f>
+        <f aca="false">IF(F60="","",IF(F60&gt;DATE(BudgetYear,12,31),"",F60))</f>
         <v/>
       </c>
       <c r="C61" s="26" t="str">
@@ -12645,7 +12689,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="36" t="str">
-        <f aca="false">IF(F61="","",IF(F61&gt;DATE(Year,12,31),"",F61))</f>
+        <f aca="false">IF(F61="","",IF(F61&gt;DATE(BudgetYear,12,31),"",F61))</f>
         <v/>
       </c>
       <c r="C62" s="26" t="str">
@@ -12667,7 +12711,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="36" t="str">
-        <f aca="false">IF(F62="","",IF(F62&gt;DATE(Year,12,31),"",F62))</f>
+        <f aca="false">IF(F62="","",IF(F62&gt;DATE(BudgetYear,12,31),"",F62))</f>
         <v/>
       </c>
       <c r="C63" s="26" t="str">
@@ -12689,7 +12733,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="36" t="str">
-        <f aca="false">IF(F63="","",IF(F63&gt;DATE(Year,12,31),"",F63))</f>
+        <f aca="false">IF(F63="","",IF(F63&gt;DATE(BudgetYear,12,31),"",F63))</f>
         <v/>
       </c>
       <c r="C64" s="26" t="str">
@@ -12755,20 +12799,21 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="11" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12799,64 +12844,64 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>100</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="17" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="C10" s="26" t="n">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="D10" s="38" t="n">
-        <v>0.2299</v>
+        <v>0</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F10" s="39" t="n">
         <f aca="false">IF(C10="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C10,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D10,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12864,33 +12909,33 @@
       </c>
       <c r="G10" s="39" t="n">
         <f aca="false">IF(OR(C10="",E10=""),"",IFERROR(ROUNDUP(NPER(D10/12,-E10,C10),0),"never: raise the minimum"))</f>
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="H10" s="22" t="n">
         <f aca="false">IF(OR(C10="",E10="",NOT(ISNUMBER(G10))),"",G10*E10-C10)</f>
-        <v>1425</v>
+        <v>0</v>
       </c>
       <c r="I10" s="39" t="n">
         <f aca="false">IF(OR(C10="",E10="",F10&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D10/12,-(E10+$C$7),C10),0),""))</f>
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J10" s="22" t="n">
         <f aca="false">IF(OR(I10="",NOT(ISNUMBER(H10))),"",MAX(0,H10-(I10*(E10+$C$7)-C10)))</f>
-        <v>850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="C11" s="26" t="n">
-        <v>8200</v>
+        <v>2400</v>
       </c>
       <c r="D11" s="38" t="n">
-        <v>0.069</v>
+        <v>0.2299</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="F11" s="39" t="n">
         <f aca="false">IF(C11="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C11,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D11,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12898,11 +12943,11 @@
       </c>
       <c r="G11" s="39" t="n">
         <f aca="false">IF(OR(C11="",E11=""),"",IFERROR(ROUNDUP(NPER(D11/12,-E11,C11),0),"never: raise the minimum"))</f>
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H11" s="22" t="n">
         <f aca="false">IF(OR(C11="",E11="",NOT(ISNUMBER(G11))),"",G11*E11-C11)</f>
-        <v>1250</v>
+        <v>1425</v>
       </c>
       <c r="I11" s="39" t="str">
         <f aca="false">IF(OR(C11="",E11="",F11&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D11/12,-(E11+$C$7),C11),0),""))</f>
@@ -12915,16 +12960,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="17" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="C12" s="26" t="n">
-        <v>14500</v>
+        <v>8200</v>
       </c>
       <c r="D12" s="38" t="n">
-        <v>0.055</v>
+        <v>0.069</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="F12" s="39" t="n">
         <f aca="false">IF(C12="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C12,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D12,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12932,11 +12977,11 @@
       </c>
       <c r="G12" s="39" t="n">
         <f aca="false">IF(OR(C12="",E12=""),"",IFERROR(ROUNDUP(NPER(D12/12,-E12,C12),0),"never: raise the minimum"))</f>
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="H12" s="22" t="n">
         <f aca="false">IF(OR(C12="",E12="",NOT(ISNUMBER(G12))),"",G12*E12-C12)</f>
-        <v>3680</v>
+        <v>1250</v>
       </c>
       <c r="I12" s="39" t="str">
         <f aca="false">IF(OR(C12="",E12="",F12&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D12/12,-(E12+$C$7),C12),0),""))</f>
@@ -12948,21 +12993,29 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="39" t="str">
+      <c r="B13" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="26" t="n">
+        <v>14500</v>
+      </c>
+      <c r="D13" s="38" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>180</v>
+      </c>
+      <c r="F13" s="39" t="n">
         <f aca="false">IF(C13="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C13,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D13,$C$10:$C$19,"&lt;&gt;")+1))</f>
-        <v/>
-      </c>
-      <c r="G13" s="39" t="str">
+        <v>4</v>
+      </c>
+      <c r="G13" s="39" t="n">
         <f aca="false">IF(OR(C13="",E13=""),"",IFERROR(ROUNDUP(NPER(D13/12,-E13,C13),0),"never: raise the minimum"))</f>
-        <v/>
-      </c>
-      <c r="H13" s="22" t="str">
+        <v>101</v>
+      </c>
+      <c r="H13" s="22" t="n">
         <f aca="false">IF(OR(C13="",E13="",NOT(ISNUMBER(G13))),"",G13*E13-C13)</f>
-        <v/>
+        <v>3680</v>
       </c>
       <c r="I13" s="39" t="str">
         <f aca="false">IF(OR(C13="",E13="",F13&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D13/12,-(E13+$C$7),C13),0),""))</f>
@@ -13131,15 +13184,15 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C20" s="23" t="n">
         <f aca="false">SUM(C10:C19)</f>
-        <v>25100</v>
+        <v>25700</v>
       </c>
       <c r="E20" s="23" t="n">
         <f aca="false">SUM(E10:E19)</f>
-        <v>465</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -13189,12 +13242,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13223,26 +13276,28 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="H6" s="10"/>
+        <v>173</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="17" t="s">
@@ -13262,17 +13317,17 @@
         <v>46722</v>
       </c>
       <c r="G7" s="22" t="n">
-        <f aca="true">IF(OR(C7="",F7=""),"",IF(D7&gt;=C7,"Reached",IF(((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C7-D7)/((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY())))))</f>
+        <f aca="true">IF(OR(C7="",F7=""),"",IF(D7&gt;=C7,"Reached",IF(((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C7-D7)/MAX(1,((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY()))))))</f>
         <v>271.428571428571</v>
       </c>
-      <c r="H7" s="33" t="str">
+      <c r="H7" s="41" t="str">
         <f aca="false">IF(E7="","",REPT("█",ROUND(MIN(1,MAX(0,E7))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E7))*10,0)))</f>
         <v>██░░░░░░░░</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C8" s="26" t="n">
         <v>1800</v>
@@ -13288,17 +13343,17 @@
         <v>46569</v>
       </c>
       <c r="G8" s="22" t="n">
-        <f aca="true">IF(OR(C8="",F8=""),"",IF(D8&gt;=C8,"Reached",IF(((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C8-D8)/((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY())))))</f>
+        <f aca="true">IF(OR(C8="",F8=""),"",IF(D8&gt;=C8,"Reached",IF(((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C8-D8)/MAX(1,((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY()))))))</f>
         <v>150</v>
       </c>
-      <c r="H8" s="33" t="str">
+      <c r="H8" s="41" t="str">
         <f aca="false">IF(E8="","",REPT("█",ROUND(MIN(1,MAX(0,E8))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E8))*10,0)))</f>
         <v>███░░░░░░░</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C9" s="26" t="n">
         <v>1200</v>
@@ -13314,10 +13369,10 @@
         <v>46631</v>
       </c>
       <c r="G9" s="22" t="n">
-        <f aca="true">IF(OR(C9="",F9=""),"",IF(D9&gt;=C9,"Reached",IF(((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C9-D9)/((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY())))))</f>
+        <f aca="true">IF(OR(C9="",F9=""),"",IF(D9&gt;=C9,"Reached",IF(((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C9-D9)/MAX(1,((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY()))))))</f>
         <v>81.8181818181818</v>
       </c>
-      <c r="H9" s="33" t="str">
+      <c r="H9" s="41" t="str">
         <f aca="false">IF(E9="","",REPT("█",ROUND(MIN(1,MAX(0,E9))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E9))*10,0)))</f>
         <v>███░░░░░░░</v>
       </c>
@@ -13332,10 +13387,10 @@
       </c>
       <c r="F10" s="40"/>
       <c r="G10" s="22" t="str">
-        <f aca="true">IF(OR(C10="",F10=""),"",IF(D10&gt;=C10,"Reached",IF(((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C10-D10)/((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H10" s="33" t="str">
+        <f aca="true">IF(OR(C10="",F10=""),"",IF(D10&gt;=C10,"Reached",IF(((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C10-D10)/MAX(1,((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="41" t="str">
         <f aca="false">IF(E10="","",REPT("█",ROUND(MIN(1,MAX(0,E10))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E10))*10,0)))</f>
         <v/>
       </c>
@@ -13350,10 +13405,10 @@
       </c>
       <c r="F11" s="40"/>
       <c r="G11" s="22" t="str">
-        <f aca="true">IF(OR(C11="",F11=""),"",IF(D11&gt;=C11,"Reached",IF(((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C11-D11)/((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H11" s="33" t="str">
+        <f aca="true">IF(OR(C11="",F11=""),"",IF(D11&gt;=C11,"Reached",IF(((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C11-D11)/MAX(1,((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="41" t="str">
         <f aca="false">IF(E11="","",REPT("█",ROUND(MIN(1,MAX(0,E11))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E11))*10,0)))</f>
         <v/>
       </c>
@@ -13368,10 +13423,10 @@
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="22" t="str">
-        <f aca="true">IF(OR(C12="",F12=""),"",IF(D12&gt;=C12,"Reached",IF(((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C12-D12)/((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H12" s="33" t="str">
+        <f aca="true">IF(OR(C12="",F12=""),"",IF(D12&gt;=C12,"Reached",IF(((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C12-D12)/MAX(1,((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="41" t="str">
         <f aca="false">IF(E12="","",REPT("█",ROUND(MIN(1,MAX(0,E12))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E12))*10,0)))</f>
         <v/>
       </c>
@@ -13386,10 +13441,10 @@
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="22" t="str">
-        <f aca="true">IF(OR(C13="",F13=""),"",IF(D13&gt;=C13,"Reached",IF(((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C13-D13)/((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H13" s="33" t="str">
+        <f aca="true">IF(OR(C13="",F13=""),"",IF(D13&gt;=C13,"Reached",IF(((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C13-D13)/MAX(1,((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="41" t="str">
         <f aca="false">IF(E13="","",REPT("█",ROUND(MIN(1,MAX(0,E13))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E13))*10,0)))</f>
         <v/>
       </c>
@@ -13404,10 +13459,10 @@
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="22" t="str">
-        <f aca="true">IF(OR(C14="",F14=""),"",IF(D14&gt;=C14,"Reached",IF(((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C14-D14)/((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H14" s="33" t="str">
+        <f aca="true">IF(OR(C14="",F14=""),"",IF(D14&gt;=C14,"Reached",IF(((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C14-D14)/MAX(1,((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="41" t="str">
         <f aca="false">IF(E14="","",REPT("█",ROUND(MIN(1,MAX(0,E14))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E14))*10,0)))</f>
         <v/>
       </c>
@@ -13422,10 +13477,10 @@
       </c>
       <c r="F15" s="40"/>
       <c r="G15" s="22" t="str">
-        <f aca="true">IF(OR(C15="",F15=""),"",IF(D15&gt;=C15,"Reached",IF(((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C15-D15)/((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H15" s="33" t="str">
+        <f aca="true">IF(OR(C15="",F15=""),"",IF(D15&gt;=C15,"Reached",IF(((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C15-D15)/MAX(1,((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="41" t="str">
         <f aca="false">IF(E15="","",REPT("█",ROUND(MIN(1,MAX(0,E15))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E15))*10,0)))</f>
         <v/>
       </c>
@@ -13440,10 +13495,10 @@
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="22" t="str">
-        <f aca="true">IF(OR(C16="",F16=""),"",IF(D16&gt;=C16,"Reached",IF(((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C16-D16)/((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H16" s="33" t="str">
+        <f aca="true">IF(OR(C16="",F16=""),"",IF(D16&gt;=C16,"Reached",IF(((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C16-D16)/MAX(1,((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="41" t="str">
         <f aca="false">IF(E16="","",REPT("█",ROUND(MIN(1,MAX(0,E16))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E16))*10,0)))</f>
         <v/>
       </c>
@@ -13525,7 +13580,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>59</v>
       </c>
@@ -13548,7 +13603,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
         <v>12</v>
       </c>
@@ -13581,7 +13636,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
         <v>15</v>
       </c>
@@ -13614,7 +13669,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
         <v>18</v>
       </c>
@@ -13647,7 +13702,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="21" t="s">
         <v>21</v>
       </c>
@@ -13680,7 +13735,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="21" t="s">
         <v>24</v>
       </c>
@@ -13713,7 +13768,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
         <v>25</v>
       </c>
@@ -13746,7 +13801,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="21" t="s">
         <v>28</v>
       </c>
@@ -13779,7 +13834,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="21" t="s">
         <v>32</v>
       </c>
@@ -13812,7 +13867,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="21" t="s">
         <v>34</v>
       </c>
@@ -13845,7 +13900,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="21" t="s">
         <v>36</v>
       </c>
@@ -13878,7 +13933,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="21" t="s">
         <v>38</v>
       </c>
@@ -13911,7 +13966,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
         <v>40</v>
       </c>
@@ -13944,7 +13999,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="19" t="s">
         <v>66</v>
       </c>
@@ -13977,7 +14032,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="19" t="s">
         <v>67</v>
       </c>
@@ -13998,7 +14053,7 @@
         <v>Savings</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H21" s="11" t="str">
         <f aca="false">IF(Setup!E24="","",Setup!E24)</f>
         <v>Sinking funds</v>
@@ -14012,7 +14067,7 @@
         <v>Savings</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H22" s="11" t="str">
         <f aca="false">IF(Setup!E25="","",Setup!E25)</f>
         <v>Retirement</v>
@@ -14046,7 +14101,7 @@
         <v>Debt</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
         <v>69</v>
       </c>
@@ -14067,7 +14122,7 @@
         <v>Debt</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="11" t="s">
         <v>70</v>
       </c>
@@ -14088,7 +14143,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="11" t="s">
         <v>9</v>
       </c>
@@ -14109,7 +14164,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="11" t="s">
         <v>8</v>
       </c>
@@ -14130,7 +14185,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H28" s="11" t="str">
         <f aca="false">IF(Setup!E31="","",Setup!E31)</f>
         <v/>
@@ -14144,7 +14199,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H29" s="11" t="str">
         <f aca="false">IF(Setup!E32="","",Setup!E32)</f>
         <v/>
@@ -14158,7 +14213,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H30" s="11" t="str">
         <f aca="false">IF(Setup!E33="","",Setup!E33)</f>
         <v/>
@@ -14172,7 +14227,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H31" s="11" t="str">
         <f aca="false">IF(Setup!E34="","",Setup!E34)</f>
         <v/>
@@ -14186,7 +14241,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H32" s="11" t="str">
         <f aca="false">IF(Setup!E35="","",Setup!E35)</f>
         <v/>
@@ -14200,7 +14255,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H33" s="11" t="str">
         <f aca="false">IF(Setup!E36="","",Setup!E36)</f>
         <v/>
@@ -14214,7 +14269,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H34" s="11" t="str">
         <f aca="false">IF(Setup!E37="","",Setup!E37)</f>
         <v/>
@@ -14228,7 +14283,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H35" s="11" t="str">
         <f aca="false">IF(Setup!E38="","",Setup!E38)</f>
         <v/>
@@ -14242,7 +14297,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H36" s="11" t="str">
         <f aca="false">IF(Setup!E39="","",Setup!E39)</f>
         <v/>
@@ -14361,7 +14416,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
         <v>74</v>
       </c>
@@ -14723,7 +14778,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -14773,7 +14828,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -14797,7 +14852,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29" t="n">
         <v>46390</v>
       </c>
@@ -14818,7 +14873,7 @@
         <v>2112.09</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29" t="n">
         <v>46391</v>
       </c>
@@ -14839,7 +14894,7 @@
         <v>1787.91</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29" t="n">
         <v>46393</v>
       </c>
@@ -14860,7 +14915,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29" t="n">
         <v>46396</v>
       </c>
@@ -14874,7 +14929,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29" t="n">
         <v>46398</v>
       </c>
@@ -14904,7 +14959,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29" t="n">
         <v>46401</v>
       </c>
@@ -14942,7 +14997,7 @@
         <v>█████████░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29" t="n">
         <v>46402</v>
       </c>
@@ -14980,7 +15035,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29" t="n">
         <v>46405</v>
       </c>
@@ -15018,7 +15073,7 @@
         <v>████░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29" t="n">
         <v>46408</v>
       </c>
@@ -15056,7 +15111,7 @@
         <v>███░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29" t="n">
         <v>46411</v>
       </c>
@@ -15094,7 +15149,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29" t="n">
         <v>46412</v>
       </c>
@@ -15132,7 +15187,7 @@
         <v>██████░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -15162,7 +15217,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -15192,7 +15247,7 @@
         <v>███░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -15222,7 +15277,7 @@
         <v>█████░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -15252,7 +15307,7 @@
         <v>████░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -15282,7 +15337,7 @@
         <v>██████████</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -15312,7 +15367,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -15342,7 +15397,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -15372,7 +15427,7 @@
         <v>██████████</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -15402,7 +15457,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -15432,7 +15487,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -15462,7 +15517,7 @@
         <v>██████████</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -15492,7 +15547,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -15522,7 +15577,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -15552,7 +15607,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -15582,7 +15637,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -15612,7 +15667,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -15642,7 +15697,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -15672,7 +15727,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -15702,7 +15757,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -15732,7 +15787,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -15762,7 +15817,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -15792,7 +15847,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -15822,7 +15877,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -15852,275 +15907,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -16170,7 +16230,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -16220,7 +16280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -16244,7 +16304,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -16257,7 +16317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -16270,7 +16330,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -16283,13 +16343,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -16311,7 +16371,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -16341,7 +16401,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -16371,7 +16431,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -16401,7 +16461,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -16431,7 +16491,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -16461,7 +16521,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -16491,7 +16551,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -16521,7 +16581,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -16551,7 +16611,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -16581,7 +16641,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -16611,7 +16671,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -16641,7 +16701,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -16671,7 +16731,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -16701,7 +16761,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -16731,7 +16791,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -16761,7 +16821,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -16791,7 +16851,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -16821,7 +16881,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -16851,7 +16911,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -16881,7 +16941,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -16911,7 +16971,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -16941,7 +17001,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -16971,7 +17031,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -17001,7 +17061,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -17031,7 +17091,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -17061,7 +17121,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -17091,7 +17151,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -17121,7 +17181,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -17151,7 +17211,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -17181,7 +17241,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -17211,275 +17271,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -17529,7 +17594,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -17579,7 +17644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -17603,7 +17668,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -17616,7 +17681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -17629,7 +17694,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -17642,13 +17707,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -17670,7 +17735,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -17700,7 +17765,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -17730,7 +17795,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -17760,7 +17825,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -17790,7 +17855,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -17820,7 +17885,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -17850,7 +17915,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -17880,7 +17945,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -17910,7 +17975,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -17940,7 +18005,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -17970,7 +18035,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -18000,7 +18065,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -18030,7 +18095,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -18060,7 +18125,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -18090,7 +18155,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -18120,7 +18185,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -18150,7 +18215,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -18180,7 +18245,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -18210,7 +18275,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -18240,7 +18305,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -18270,7 +18335,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -18300,7 +18365,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -18330,7 +18395,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -18360,7 +18425,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -18390,7 +18455,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -18420,7 +18485,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -18450,7 +18515,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -18480,7 +18545,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -18510,7 +18575,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -18540,7 +18605,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -18570,275 +18635,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -18888,7 +18958,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -18938,7 +19008,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -18962,7 +19032,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -18975,7 +19045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -18988,7 +19058,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -19001,13 +19071,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -19029,7 +19099,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -19059,7 +19129,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -19089,7 +19159,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -19119,7 +19189,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -19149,7 +19219,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -19179,7 +19249,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -19209,7 +19279,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -19239,7 +19309,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -19269,7 +19339,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -19299,7 +19369,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -19329,7 +19399,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -19359,7 +19429,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -19389,7 +19459,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -19419,7 +19489,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -19449,7 +19519,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -19479,7 +19549,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -19509,7 +19579,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -19539,7 +19609,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -19569,7 +19639,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -19599,7 +19669,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -19629,7 +19699,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -19659,7 +19729,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -19689,7 +19759,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -19719,7 +19789,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -19749,7 +19819,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -19779,7 +19849,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -19809,7 +19879,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -19839,7 +19909,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -19869,7 +19939,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -19899,7 +19969,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -19929,275 +19999,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -20247,7 +20322,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -20297,7 +20372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -20321,7 +20396,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -20334,7 +20409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -20347,7 +20422,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -20360,13 +20435,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -20388,7 +20463,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -20418,7 +20493,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -20448,7 +20523,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -20478,7 +20553,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -20508,7 +20583,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -20538,7 +20613,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -20568,7 +20643,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -20598,7 +20673,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -20628,7 +20703,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -20658,7 +20733,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -20688,7 +20763,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -20718,7 +20793,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -20748,7 +20823,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -20778,7 +20853,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -20808,7 +20883,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -20838,7 +20913,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -20868,7 +20943,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -20898,7 +20973,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -20928,7 +21003,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -20958,7 +21033,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -20988,7 +21063,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -21018,7 +21093,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -21048,7 +21123,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -21078,7 +21153,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -21108,7 +21183,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -21138,7 +21213,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -21168,7 +21243,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -21198,7 +21273,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -21228,7 +21303,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -21258,7 +21333,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -21288,275 +21363,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -21606,7 +21686,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -21656,7 +21736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -21680,7 +21760,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -21693,7 +21773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -21706,7 +21786,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -21719,13 +21799,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -21747,7 +21827,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -21777,7 +21857,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -21807,7 +21887,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -21837,7 +21917,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -21867,7 +21947,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -21897,7 +21977,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -21927,7 +22007,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -21957,7 +22037,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -21987,7 +22067,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -22017,7 +22097,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -22047,7 +22127,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -22077,7 +22157,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -22107,7 +22187,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -22137,7 +22217,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -22167,7 +22247,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -22197,7 +22277,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -22227,7 +22307,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -22257,7 +22337,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -22287,7 +22367,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -22317,7 +22397,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -22347,7 +22427,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -22377,7 +22457,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -22407,7 +22487,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -22437,7 +22517,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -22467,7 +22547,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -22497,7 +22577,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -22527,7 +22607,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -22557,7 +22637,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -22587,7 +22667,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -22617,7 +22697,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -22647,275 +22727,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>

--- a/data/products/p-gsb-001/work/views/calc/Clear-Budget.xlsx
+++ b/data/products/p-gsb-001/work/views/calc/Clear-Budget.xlsx
@@ -552,7 +552,7 @@
     <t xml:space="preserve">Interest saved</t>
   </si>
   <si>
-    <t xml:space="preserve">Medical bill</t>
+    <t xml:space="preserve">Store card</t>
   </si>
   <si>
     <t xml:space="preserve">Car loan</t>
@@ -1366,11 +1366,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="14989513"/>
-        <c:axId val="2526117"/>
+        <c:axId val="70405691"/>
+        <c:axId val="32507998"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="14989513"/>
+        <c:axId val="70405691"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1402,7 +1402,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2526117"/>
+        <c:crossAx val="32507998"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1410,7 +1410,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2526117"/>
+        <c:axId val="32507998"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1452,7 +1452,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14989513"/>
+        <c:crossAx val="70405691"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1872,7 +1872,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>858240</xdr:colOff>
+      <xdr:colOff>505800</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>42120</xdr:rowOff>
     </xdr:to>
@@ -10939,7 +10939,7 @@
       <c r="D7" s="26" t="n">
         <v>1400</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="34" t="s">
         <v>134</v>
       </c>
       <c r="F7" s="34"/>
@@ -10965,7 +10965,7 @@
       <c r="D8" s="26" t="n">
         <v>95</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="34" t="s">
         <v>134</v>
       </c>
       <c r="F8" s="34"/>
@@ -10991,7 +10991,7 @@
       <c r="D9" s="26" t="n">
         <v>15.99</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="34" t="s">
         <v>134</v>
       </c>
       <c r="F9" s="34"/>
@@ -11017,7 +11017,7 @@
       <c r="D10" s="26" t="n">
         <v>160</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="34" t="s">
         <v>136</v>
       </c>
       <c r="F10" s="34"/>
@@ -11043,7 +11043,7 @@
       <c r="D11" s="26" t="n">
         <v>90</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="34" t="s">
         <v>136</v>
       </c>
       <c r="F11" s="34"/>
@@ -11069,7 +11069,7 @@
       <c r="D12" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="34" t="s">
         <v>136</v>
       </c>
       <c r="F12" s="34"/>
@@ -11089,7 +11089,7 @@
       <c r="B13" s="17"/>
       <c r="C13" s="25"/>
       <c r="D13" s="26"/>
-      <c r="E13" s="17"/>
+      <c r="E13" s="34"/>
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="34"/>
@@ -11107,7 +11107,7 @@
       <c r="B14" s="17"/>
       <c r="C14" s="25"/>
       <c r="D14" s="26"/>
-      <c r="E14" s="17"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
       <c r="H14" s="34"/>
@@ -11125,7 +11125,7 @@
       <c r="B15" s="17"/>
       <c r="C15" s="25"/>
       <c r="D15" s="26"/>
-      <c r="E15" s="17"/>
+      <c r="E15" s="34"/>
       <c r="F15" s="34"/>
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
@@ -11143,7 +11143,7 @@
       <c r="B16" s="17"/>
       <c r="C16" s="25"/>
       <c r="D16" s="26"/>
-      <c r="E16" s="17"/>
+      <c r="E16" s="34"/>
       <c r="F16" s="34"/>
       <c r="G16" s="34"/>
       <c r="H16" s="34"/>
@@ -11161,7 +11161,7 @@
       <c r="B17" s="17"/>
       <c r="C17" s="25"/>
       <c r="D17" s="26"/>
-      <c r="E17" s="17"/>
+      <c r="E17" s="34"/>
       <c r="F17" s="34"/>
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
@@ -11179,7 +11179,7 @@
       <c r="B18" s="17"/>
       <c r="C18" s="25"/>
       <c r="D18" s="26"/>
-      <c r="E18" s="17"/>
+      <c r="E18" s="34"/>
       <c r="F18" s="34"/>
       <c r="G18" s="34"/>
       <c r="H18" s="34"/>
@@ -11197,7 +11197,7 @@
       <c r="B19" s="17"/>
       <c r="C19" s="25"/>
       <c r="D19" s="26"/>
-      <c r="E19" s="17"/>
+      <c r="E19" s="34"/>
       <c r="F19" s="34"/>
       <c r="G19" s="34"/>
       <c r="H19" s="34"/>
@@ -11215,7 +11215,7 @@
       <c r="B20" s="17"/>
       <c r="C20" s="25"/>
       <c r="D20" s="26"/>
-      <c r="E20" s="17"/>
+      <c r="E20" s="34"/>
       <c r="F20" s="34"/>
       <c r="G20" s="34"/>
       <c r="H20" s="34"/>
@@ -11233,7 +11233,7 @@
       <c r="B21" s="17"/>
       <c r="C21" s="25"/>
       <c r="D21" s="26"/>
-      <c r="E21" s="17"/>
+      <c r="E21" s="34"/>
       <c r="F21" s="34"/>
       <c r="G21" s="34"/>
       <c r="H21" s="34"/>
@@ -11251,7 +11251,7 @@
       <c r="B22" s="17"/>
       <c r="C22" s="25"/>
       <c r="D22" s="26"/>
-      <c r="E22" s="17"/>
+      <c r="E22" s="34"/>
       <c r="F22" s="34"/>
       <c r="G22" s="34"/>
       <c r="H22" s="34"/>
@@ -11269,7 +11269,7 @@
       <c r="B23" s="17"/>
       <c r="C23" s="25"/>
       <c r="D23" s="26"/>
-      <c r="E23" s="17"/>
+      <c r="E23" s="34"/>
       <c r="F23" s="34"/>
       <c r="G23" s="34"/>
       <c r="H23" s="34"/>
@@ -11287,7 +11287,7 @@
       <c r="B24" s="17"/>
       <c r="C24" s="25"/>
       <c r="D24" s="26"/>
-      <c r="E24" s="17"/>
+      <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="34"/>
       <c r="H24" s="34"/>
@@ -11305,7 +11305,7 @@
       <c r="B25" s="17"/>
       <c r="C25" s="25"/>
       <c r="D25" s="26"/>
-      <c r="E25" s="17"/>
+      <c r="E25" s="34"/>
       <c r="F25" s="34"/>
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
@@ -11323,7 +11323,7 @@
       <c r="B26" s="17"/>
       <c r="C26" s="25"/>
       <c r="D26" s="26"/>
-      <c r="E26" s="17"/>
+      <c r="E26" s="34"/>
       <c r="F26" s="34"/>
       <c r="G26" s="34"/>
       <c r="H26" s="34"/>
@@ -11341,7 +11341,7 @@
       <c r="B27" s="17"/>
       <c r="C27" s="25"/>
       <c r="D27" s="26"/>
-      <c r="E27" s="17"/>
+      <c r="E27" s="34"/>
       <c r="F27" s="34"/>
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
@@ -11359,7 +11359,7 @@
       <c r="B28" s="17"/>
       <c r="C28" s="25"/>
       <c r="D28" s="26"/>
-      <c r="E28" s="17"/>
+      <c r="E28" s="34"/>
       <c r="F28" s="34"/>
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
@@ -11377,7 +11377,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="25"/>
       <c r="D29" s="26"/>
-      <c r="E29" s="17"/>
+      <c r="E29" s="34"/>
       <c r="F29" s="34"/>
       <c r="G29" s="34"/>
       <c r="H29" s="34"/>
@@ -11395,7 +11395,7 @@
       <c r="B30" s="17"/>
       <c r="C30" s="25"/>
       <c r="D30" s="26"/>
-      <c r="E30" s="17"/>
+      <c r="E30" s="34"/>
       <c r="F30" s="34"/>
       <c r="G30" s="34"/>
       <c r="H30" s="34"/>
@@ -11413,7 +11413,7 @@
       <c r="B31" s="17"/>
       <c r="C31" s="25"/>
       <c r="D31" s="26"/>
-      <c r="E31" s="17"/>
+      <c r="E31" s="34"/>
       <c r="F31" s="34"/>
       <c r="G31" s="34"/>
       <c r="H31" s="34"/>
@@ -12898,10 +12898,10 @@
         <v>600</v>
       </c>
       <c r="D10" s="38" t="n">
-        <v>0</v>
+        <v>0.1999</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F10" s="39" t="n">
         <f aca="false">IF(C10="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C10,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D10,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12909,19 +12909,19 @@
       </c>
       <c r="G10" s="39" t="n">
         <f aca="false">IF(OR(C10="",E10=""),"",IFERROR(ROUNDUP(NPER(D10/12,-E10,C10),0),"never: raise the minimum"))</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H10" s="22" t="n">
         <f aca="false">IF(OR(C10="",E10="",NOT(ISNUMBER(G10))),"",G10*E10-C10)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I10" s="39" t="n">
         <f aca="false">IF(OR(C10="",E10="",F10&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D10/12,-(E10+$C$7),C10),0),""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" s="22" t="n">
         <f aca="false">IF(OR(I10="",NOT(ISNUMBER(H10))),"",MAX(0,H10-(I10*(E10+$C$7)-C10)))</f>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12932,7 +12932,7 @@
         <v>2400</v>
       </c>
       <c r="D11" s="38" t="n">
-        <v>0.2299</v>
+        <v>0.2499</v>
       </c>
       <c r="E11" s="26" t="n">
         <v>75</v>
@@ -12943,11 +12943,11 @@
       </c>
       <c r="G11" s="39" t="n">
         <f aca="false">IF(OR(C11="",E11=""),"",IFERROR(ROUNDUP(NPER(D11/12,-E11,C11),0),"never: raise the minimum"))</f>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H11" s="22" t="n">
         <f aca="false">IF(OR(C11="",E11="",NOT(ISNUMBER(G11))),"",G11*E11-C11)</f>
-        <v>1425</v>
+        <v>1650</v>
       </c>
       <c r="I11" s="39" t="str">
         <f aca="false">IF(OR(C11="",E11="",F11&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D11/12,-(E11+$C$7),C11),0),""))</f>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="E20" s="23" t="n">
         <f aca="false">SUM(E10:E19)</f>
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -13536,7 +13536,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
